--- a/innolight/dist/20261025_中際旭創模型_v0.2.xlsx
+++ b/innolight/dist/20261025_中際旭創模型_v0.2.xlsx
@@ -4422,7 +4422,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4659,7 +4659,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4780,7 +4780,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4901,7 +4901,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5022,7 +5022,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5143,7 +5143,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
